--- a/Result/profitability/7842.xlsx
+++ b/Result/profitability/7842.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM9"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,7 +1118,7 @@
         <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1147,10 +1147,10 @@
         <v>114.2</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2999999999999999</v>
+        <v>0.2799999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3111111111111111</v>
       </c>
       <c r="Y6" t="n">
         <v>-0.8499999999999996</v>
@@ -1159,10 +1159,10 @@
         <v>-0.1473136915077989</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.68</v>
+        <v>-1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.5833333333333333</v>
+        <v>-0.5902777777777778</v>
       </c>
       <c r="AC6" t="n">
         <v>-0.09999999999999964</v>
@@ -1270,10 +1270,10 @@
         <v>114.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02000000000000002</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01666666666666661</v>
+        <v>0.03389830508474589</v>
       </c>
       <c r="Y7" t="n">
         <v>0.7700000000000005</v>
@@ -1490,7 +1490,7 @@
         <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3675</v>
+        <v>1.365</v>
       </c>
       <c r="N9" t="n">
         <v>5.3625</v>
@@ -1571,6 +1571,133 @@
       </c>
       <c r="AM9" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7842</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>954</v>
+      </c>
+      <c r="D10" t="n">
+        <v>893</v>
+      </c>
+      <c r="E10" t="n">
+        <v>61</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="G10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4.20%</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" t="n">
+        <v>32</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.23875</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5.53125</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.4060150375939851</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.8899999999999997</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.1624087591240875</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.6900000000000002</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.5847457627118646</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.2947154471544715</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
